--- a/kpi/2026-09/9월 온라인 KPI_수정본.xlsx
+++ b/kpi/2026-09/9월 온라인 KPI_수정본.xlsx
@@ -588,7 +588,7 @@
       <c r="O9" s="7" t="inlineStr">
         <is>
           <t>매출 85.6%
-이익률 19.2%
+이익률 19.6%
 (목표 20%)</t>
         </is>
       </c>
@@ -674,8 +674,8 @@
 ━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━
 ① [매출/수익성 핵심 요약]
 ▶ 미유박스 영업이익 16,703,049원 / 마진율 15.4% (8월 29.8% → -14.4%p)
-▶ 핫팩 및 기타 영업이익 9,661,715원 / 마진율 34.1% — 시즌 진입과 함께 매출·수익 동시 확대
-▶ 합산 영업이익 26,364,764원 / 합산 마진율 19.2% — 8월 30.2% 대비 -11.0%p
+▶ 핫팩 및 기타 영업이익 10,216,114원 / 마진율 36.1% — 시즌 진입과 함께 매출·수익 동시 확대
+▶ 합산 영업이익 26,919,164원 / 합산 마진율 19.6% — 8월 30.2% 대비 -10.6%p
 ▶ 총 광고비 18,361,945원 (8월 13,973,397원 대비 +31.4%)
 ▶ 미유박스 광고비 17,348,818원 / 매출 대비 16.0% — 광고비 상승 대비 매출 감소로 효율 재점검 필요
 ② [채널 운영 주요 이슈]
@@ -683,7 +683,7 @@
 ▶ 쿠팡 WING(신우) 24,567,370원 / 15.9%, WING(미유) 13,310,740원 / 15.3% — 수익성 방어 필요
 ▶ 자사몰(미유박스) 16,152,734원 / 24.2% — 안정적 수익 채널, CRM·재구매 강화 대상
 ▶ 펫프렌즈 3P -29.5%, 11번가 6.7%, 지마켓 1.3%, 펫프렌즈 직매입 3.7% — 저효율 채널 구조 개선 필요
-▶ 핫팩 스마트스토어 18,471,410원 / 40.5%, 마켓컬리 샛별배송 3,364,100원 / 43.8%, 자사몰 39.1%로 고수익 채널 확보
+▶ 핫팩 스마트스토어 18,471,410원 / 40.5%, 마켓컬리 샛별배송 3,364,100원 / 60.3%, 자사몰 39.1%로 고수익 채널 확보
 ▶ 핫팩 지마켓 -18.9%, 쿠팡 WING(신우) -22.0% — 시즌 확대 전 광고·원가·수수료 구조 즉시 조정
 ③ [상품·판매수량 및 프로젝트 진행]
 ▶ 미유박스 9월 판매수량 4,067개 (8월 6,038개, -32.6%) — 판매량 하락 원인 점검 필요
@@ -692,7 +692,7 @@
 ▶ 내손에 핫한 160g 14,140개, 히트템 포유 90g 11,580개가 시즌 초반 판매 견인
 ▶ 10월 성수기 확대를 위한 재고·검색광고·프로모션·채널별 가격정책 사전 정비 필요
 ④ [다음달 핵심 과제]
-▶ 합산 마진율 19.2% → 20% 이상 우선 회복, 미유박스 광고비율 및 저마진 채널 구조 개선
+▶ 합산 마진율 19.6% → 20% 이상 우선 회복, 미유박스 광고비율 및 저마진 채널 구조 개선
 ▶ 미유박스 핵심 상품 판매량 회복 — 스마트스토어·자사몰 중심 CRM/재구매/프로모션 강화
 ▶ 핫팩 성수기 매출 확대와 동시에 지마켓·쿠팡 WING 역마진 차단
 ▶ 10월 시즌 프로모션, 재고 회전, 광고 예산을 주 단위 KPI로 관리</t>
@@ -713,8 +713,8 @@
           <t>매출 85.6%
 (137,007,028
 /160,000,000)
-이익률 96%
-(19.2%/20%)</t>
+이익률 98%
+(19.6%/20%)</t>
         </is>
       </c>
     </row>
@@ -974,16 +974,16 @@
    - 울티메이트 11.8kg 1,297개, 옐로우 좁쌀 710개 중심 — 핵심 SKU 판매량 회복 필요
 2. [광고비/수익성] 채널별 비용 효율 점검
    - 미유박스 광고비 17,348,818원 / 핫팩 및 기타 1,013,127원 / 총 광고비 18,361,945원
-   - 총 광고비는 8월 대비 +31.4% 증가, 합산 마진율은 30.2% → 19.2% 하락
+   - 총 광고비는 8월 대비 +31.4% 증가, 합산 마진율은 30.2% → 19.6% 하락
    - 미유박스: 펫프렌즈 3P(-29.5%), 11번가(6.7%), 지마켓(1.3%), 직매입(3.7%) 개선 필요
    - 핫팩: 지마켓(-18.9%), 쿠팡WING 신우(-22.0%) 역마진 즉시 조정
 3. [핫팩 시즌 운영] 성수기 전환 성과 및 실행
-   - 핫팩 및 기타 매출 28,319,705원 / 영업이익 9,661,715원 / 마진율 34.1%
+   - 핫팩 및 기타 매출 28,319,705원 / 영업이익 10,216,114원 / 마진율 36.1%
    - 전월비 매출 +257.7%, 판매수량 44,353개(+166.2%)로 시즌 진입 확인
-   - 스마트스토어 1,847만원(40.5%), 마켓컬리 샛별배송 336만원(43.8%), 자사몰 168만원(39.1%) 고마진 유지
+   - 스마트스토어 1,847만원(40.5%), 마켓컬리 샛별배송 336만원(60.3%), 자사몰 168만원(39.1%) 고마진 유지
    - 내손에 핫한 160g 14,140개 / 히트템 포유 90g 11,580개 판매로 주력 SKU 확정
 4. [전사/팀 운영] 월간 보고 및 10월 계획 수립
-   - 온라인팀 총 매출 137,007,028원 / 영업이익 26,364,764원 / 합산 마진율 19.2%
+   - 온라인팀 총 매출 137,007,028원 / 영업이익 26,919,164원 / 합산 마진율 19.6%
    - 9월 목표 매출 1.6억원 대비 85.6% 달성 — 매출·마진 모두 목표 미달
    - 10월은 미유박스 수익성 회복과 핫팩 성수기 매출 확대를 투트랙 KPI로 운영
    - 채널별 매출·광고비·마진율·판매수량을 주 단위 점검하고 역마진 채널 즉시 조정</t>
@@ -1439,7 +1439,7 @@
    - 9월 판매 770개 → 36개(-95%), 품절/공급 이슈 여부 확인 요청
 3. 직매입 채널 손익 기준 정리
    - 쿠팡·펫프렌즈 직매입, 컬리 샛별배송 수수료(약 293만원) 이익 미반영
-   - 판매가 기준이면 합산 이익률 19.2% → 17.1%, 정산 기준 확정 요청
+   - 판매가 기준이면 합산 이익률 19.6% → 17.5%, 정산 기준 확정 요청
 4. 저효율 채널 광고 축소 승인
    - 역마진 5개 채널 광고비 406만원 → 10월 축소/중단, 핫팩 스마트스토어로 재배치</t>
         </is>
